--- a/data/file_generation/reference/data_136/员工工时分配表_已填充_res.xlsx
+++ b/data/file_generation/reference/data_136/员工工时分配表_已填充_res.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tianjiaojiao/Desktop/田姣姣/output/data_136/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7281C5D2-9F3D-2344-B03C-40D4256DC076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE64C17F-9CE2-A04A-A72E-0C57C8014D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34020" yWindow="2340" windowWidth="29400" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工时统计" sheetId="3" r:id="rId1"/>
@@ -62,122 +62,124 @@
     <t>物流园区能耗与碳排数智平台示范项目</t>
   </si>
   <si>
-    <t>新海轮渡智慧配电安全集中监测
+    <t>县电力公司配电监测（30套）</t>
+  </si>
+  <si>
+    <t>综合数智能源运营服务平台接入及远程运维服务项目合同</t>
+  </si>
+  <si>
+    <t>未有项目预算的接入光伏项目</t>
+  </si>
+  <si>
+    <t>天津公司本部绩效考核系统</t>
+  </si>
+  <si>
+    <t>信息化运维服务项目1</t>
+  </si>
+  <si>
+    <t>综合数智能源运营服务平台功能深化委托研发项目合同</t>
+  </si>
+  <si>
+    <t>车联网运营平台</t>
+  </si>
+  <si>
+    <t>基于物流供应链的AI+业能（源）融合一体化智能应用研究</t>
+  </si>
+  <si>
+    <t>基于配置模型驱动的低(零)代码开发技术研究</t>
+  </si>
+  <si>
+    <t>通用配电监测装置及平台研发</t>
+  </si>
+  <si>
+    <t>基于组态化在线监测及能源管理平台研发</t>
+  </si>
+  <si>
+    <t>AI智能视觉及通用智能体技术研究</t>
+  </si>
+  <si>
+    <t>管理费</t>
+  </si>
+  <si>
+    <t>石油公司油库安全风险智能化管控平台信息系统研发及应用项目</t>
+  </si>
+  <si>
+    <t>CIM展厅零碳数据链路闭环(CIM系统扩展升级)建设项目</t>
+  </si>
+  <si>
+    <t>综合数智能源运营服务平台（二期）委托研发项目</t>
+  </si>
+  <si>
+    <t>信息化系统国产化改造项目</t>
+  </si>
+  <si>
+    <t>信息化运维服务项目2</t>
+  </si>
+  <si>
+    <t>水泥制品项目</t>
+  </si>
+  <si>
+    <t>王A</t>
+  </si>
+  <si>
+    <t>贾A</t>
+  </si>
+  <si>
+    <t>常A</t>
+  </si>
+  <si>
+    <t>黄A</t>
+  </si>
+  <si>
+    <t>代A</t>
+  </si>
+  <si>
+    <t>姜A</t>
+  </si>
+  <si>
+    <t>周A</t>
+  </si>
+  <si>
+    <t>王B</t>
+  </si>
+  <si>
+    <t>张A</t>
+  </si>
+  <si>
+    <t>赵A</t>
+  </si>
+  <si>
+    <t>田A</t>
+  </si>
+  <si>
+    <t>陈A</t>
+  </si>
+  <si>
+    <t>于A</t>
+  </si>
+  <si>
+    <t>只A</t>
+  </si>
+  <si>
+    <t>薛A</t>
+  </si>
+  <si>
+    <t>李A</t>
+  </si>
+  <si>
+    <t>蔡A</t>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AA轮渡智慧配电安全集中监测
 系统项目</t>
-  </si>
-  <si>
-    <t>县电力公司配电监测（30套）</t>
-  </si>
-  <si>
-    <t>综合数智能源运营服务平台接入及远程运维服务项目合同</t>
-  </si>
-  <si>
-    <t>未有项目预算的接入光伏项目</t>
-  </si>
-  <si>
-    <t>天津公司本部绩效考核系统</t>
-  </si>
-  <si>
-    <t>信息化运维服务项目1</t>
-  </si>
-  <si>
-    <t>综合数智能源运营服务平台功能深化委托研发项目合同</t>
-  </si>
-  <si>
-    <t>车联网运营平台</t>
-  </si>
-  <si>
-    <t>基于物流供应链的AI+业能（源）融合一体化智能应用研究</t>
-  </si>
-  <si>
-    <t>基于配置模型驱动的低(零)代码开发技术研究</t>
-  </si>
-  <si>
-    <t>通用配电监测装置及平台研发</t>
-  </si>
-  <si>
-    <t>基于组态化在线监测及能源管理平台研发</t>
-  </si>
-  <si>
-    <t>AI智能视觉及通用智能体技术研究</t>
-  </si>
-  <si>
-    <t>管理费</t>
-  </si>
-  <si>
-    <t>石油公司油库安全风险智能化管控平台信息系统研发及应用项目</t>
-  </si>
-  <si>
-    <t>CIM展厅零碳数据链路闭环(CIM系统扩展升级)建设项目</t>
-  </si>
-  <si>
-    <t>综合数智能源运营服务平台（二期）委托研发项目</t>
-  </si>
-  <si>
-    <t>信息化系统国产化改造项目</t>
-  </si>
-  <si>
-    <t>信息化运维服务项目2</t>
-  </si>
-  <si>
-    <t>水泥制品项目</t>
-  </si>
-  <si>
-    <t>滨海远宾仓储</t>
-  </si>
-  <si>
-    <t>王A</t>
-  </si>
-  <si>
-    <t>贾A</t>
-  </si>
-  <si>
-    <t>常A</t>
-  </si>
-  <si>
-    <t>黄A</t>
-  </si>
-  <si>
-    <t>代A</t>
-  </si>
-  <si>
-    <t>姜A</t>
-  </si>
-  <si>
-    <t>周A</t>
-  </si>
-  <si>
-    <t>王B</t>
-  </si>
-  <si>
-    <t>张A</t>
-  </si>
-  <si>
-    <t>赵A</t>
-  </si>
-  <si>
-    <t>田A</t>
-  </si>
-  <si>
-    <t>陈A</t>
-  </si>
-  <si>
-    <t>于A</t>
-  </si>
-  <si>
-    <t>只A</t>
-  </si>
-  <si>
-    <t>薛A</t>
-  </si>
-  <si>
-    <t>李A</t>
-  </si>
-  <si>
-    <t>蔡A</t>
-  </si>
-  <si>
-    <t>-</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BB远宾仓储</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -295,9 +297,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -312,6 +311,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -599,56 +601,56 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="N1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="Q1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="R1" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>45</v>
       </c>
       <c r="S1" s="2" t="s">
         <v>1</v>
@@ -783,8 +785,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S3" s="9" t="s">
-        <v>46</v>
+      <c r="S3" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="30">
@@ -918,8 +920,8 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S5" s="9" t="s">
-        <v>46</v>
+      <c r="S5" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1053,8 +1055,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S7" s="9" t="s">
-        <v>46</v>
+      <c r="S7" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="30">
@@ -1188,8 +1190,8 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S9" s="9" t="s">
-        <v>46</v>
+      <c r="S9" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1306,13 +1308,13 @@
       <c r="R11" s="3">
         <v>0</v>
       </c>
-      <c r="S11" s="9" t="s">
-        <v>46</v>
+      <c r="S11" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="32">
-      <c r="A12" s="4" t="s">
-        <v>8</v>
+      <c r="A12" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="B12" s="2">
         <v>0</v>
@@ -1424,13 +1426,13 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-      <c r="S13" s="9" t="s">
-        <v>46</v>
+      <c r="S13" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -1559,13 +1561,13 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S15" s="9" t="s">
-        <v>46</v>
+      <c r="S15" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="30">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2">
         <v>9</v>
@@ -1694,13 +1696,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S17" s="9" t="s">
-        <v>46</v>
+      <c r="S17" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="2">
         <v>0</v>
@@ -1812,13 +1814,13 @@
       <c r="R19" s="3">
         <v>0</v>
       </c>
-      <c r="S19" s="9" t="s">
-        <v>46</v>
+      <c r="S19" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" s="2">
         <v>8</v>
@@ -1947,13 +1949,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S21" s="9" t="s">
-        <v>46</v>
+      <c r="S21" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:19">
       <c r="A22" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" s="2">
         <v>3</v>
@@ -2082,13 +2084,13 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="S23" s="9" t="s">
-        <v>46</v>
+      <c r="S23" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="30">
       <c r="A24" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" s="2">
         <v>3</v>
@@ -2217,13 +2219,13 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S25" s="9" t="s">
-        <v>46</v>
+      <c r="S25" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="5" t="s">
-        <v>15</v>
+      <c r="A26" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="B26" s="2">
         <v>0</v>
@@ -2335,13 +2337,13 @@
       <c r="R27" s="3">
         <v>0</v>
       </c>
-      <c r="S27" s="9" t="s">
-        <v>46</v>
+      <c r="S27" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="30">
-      <c r="A28" s="5" t="s">
-        <v>16</v>
+      <c r="A28" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="B28" s="2">
         <v>10</v>
@@ -2470,13 +2472,13 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S29" s="9" t="s">
-        <v>46</v>
+      <c r="S29" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="30">
-      <c r="A30" s="5" t="s">
-        <v>17</v>
+      <c r="A30" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="B30" s="2">
         <v>36</v>
@@ -2605,13 +2607,13 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S31" s="9" t="s">
-        <v>46</v>
+      <c r="S31" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:19">
-      <c r="A32" s="5" t="s">
-        <v>18</v>
+      <c r="A32" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="B32" s="2">
         <v>43</v>
@@ -2740,13 +2742,13 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S33" s="9" t="s">
-        <v>46</v>
+      <c r="S33" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:19">
-      <c r="A34" s="5" t="s">
-        <v>19</v>
+      <c r="A34" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="B34" s="2">
         <v>60</v>
@@ -2873,13 +2875,13 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S35" s="9" t="s">
-        <v>46</v>
+      <c r="S35" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="5" t="s">
-        <v>20</v>
+      <c r="A36" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="B36" s="2">
         <v>19</v>
@@ -3008,13 +3010,13 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S37" s="9" t="s">
-        <v>46</v>
+      <c r="S37" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:19">
       <c r="A38" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B38" s="2">
         <v>0</v>
@@ -3143,13 +3145,13 @@
         <f t="shared" si="14"/>
         <v>0.21229991575400167</v>
       </c>
-      <c r="S39" s="9" t="s">
-        <v>46</v>
+      <c r="S39" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="30">
       <c r="A40" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B40" s="2">
         <v>9</v>
@@ -3278,13 +3280,13 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="S41" s="9" t="s">
-        <v>46</v>
+      <c r="S41" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="30">
       <c r="A42" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B42" s="2">
         <v>0</v>
@@ -3413,13 +3415,13 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="S43" s="9" t="s">
-        <v>46</v>
+      <c r="S43" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="30">
       <c r="A44" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B44" s="2">
         <v>8</v>
@@ -3548,13 +3550,13 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="S45" s="9" t="s">
-        <v>46</v>
+      <c r="S45" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:19">
       <c r="A46" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B46" s="2">
         <v>0</v>
@@ -3666,13 +3668,13 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="9" t="s">
-        <v>46</v>
+      <c r="S47" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:19">
       <c r="A48" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B48" s="2">
         <v>6</v>
@@ -3801,63 +3803,63 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="S49" s="9" t="s">
-        <v>46</v>
+      <c r="S49" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B50" s="7">
-        <v>0</v>
-      </c>
-      <c r="C50" s="7">
-        <v>0</v>
-      </c>
-      <c r="D50" s="7">
-        <v>0</v>
-      </c>
-      <c r="E50" s="7">
+      <c r="A50" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="6">
+        <v>0</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0</v>
+      </c>
+      <c r="D50" s="6">
+        <v>0</v>
+      </c>
+      <c r="E50" s="6">
         <v>3</v>
       </c>
-      <c r="F50" s="7">
-        <v>0</v>
-      </c>
-      <c r="G50" s="7">
-        <v>0</v>
-      </c>
-      <c r="H50" s="7">
-        <v>0</v>
-      </c>
-      <c r="I50" s="7">
-        <v>0</v>
-      </c>
-      <c r="J50" s="7">
-        <v>0</v>
-      </c>
-      <c r="K50" s="7">
-        <v>0</v>
-      </c>
-      <c r="L50" s="7">
-        <v>0</v>
-      </c>
-      <c r="M50" s="7">
-        <v>0</v>
-      </c>
-      <c r="N50" s="7">
-        <v>0</v>
-      </c>
-      <c r="O50" s="7">
-        <v>0</v>
-      </c>
-      <c r="P50" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="7">
-        <v>0</v>
-      </c>
-      <c r="R50" s="7">
+      <c r="F50" s="6">
+        <v>0</v>
+      </c>
+      <c r="G50" s="6">
+        <v>0</v>
+      </c>
+      <c r="H50" s="6">
+        <v>0</v>
+      </c>
+      <c r="I50" s="6">
+        <v>0</v>
+      </c>
+      <c r="J50" s="6">
+        <v>0</v>
+      </c>
+      <c r="K50" s="6">
+        <v>0</v>
+      </c>
+      <c r="L50" s="6">
+        <v>0</v>
+      </c>
+      <c r="M50" s="6">
+        <v>0</v>
+      </c>
+      <c r="N50" s="6">
+        <v>0</v>
+      </c>
+      <c r="O50" s="6">
+        <v>0</v>
+      </c>
+      <c r="P50" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>0</v>
+      </c>
+      <c r="R50" s="6">
         <v>0</v>
       </c>
       <c r="S50" s="2">
@@ -3936,63 +3938,63 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="S51" s="9" t="s">
+      <c r="S51" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19">
+      <c r="A52" s="5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="52" spans="1:19">
-      <c r="A52" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B52" s="7">
-        <v>0</v>
-      </c>
-      <c r="C52" s="7">
-        <v>0</v>
-      </c>
-      <c r="D52" s="7">
-        <v>0</v>
-      </c>
-      <c r="E52" s="7">
-        <v>0</v>
-      </c>
-      <c r="F52" s="7">
-        <v>0</v>
-      </c>
-      <c r="G52" s="7">
-        <v>0</v>
-      </c>
-      <c r="H52" s="7">
-        <v>0</v>
-      </c>
-      <c r="I52" s="7">
-        <v>0</v>
-      </c>
-      <c r="J52" s="7">
-        <v>0</v>
-      </c>
-      <c r="K52" s="7">
-        <v>0</v>
-      </c>
-      <c r="L52" s="7">
-        <v>0</v>
-      </c>
-      <c r="M52" s="7">
+      <c r="B52" s="6">
+        <v>0</v>
+      </c>
+      <c r="C52" s="6">
+        <v>0</v>
+      </c>
+      <c r="D52" s="6">
+        <v>0</v>
+      </c>
+      <c r="E52" s="6">
+        <v>0</v>
+      </c>
+      <c r="F52" s="6">
+        <v>0</v>
+      </c>
+      <c r="G52" s="6">
+        <v>0</v>
+      </c>
+      <c r="H52" s="6">
+        <v>0</v>
+      </c>
+      <c r="I52" s="6">
+        <v>0</v>
+      </c>
+      <c r="J52" s="6">
+        <v>0</v>
+      </c>
+      <c r="K52" s="6">
+        <v>0</v>
+      </c>
+      <c r="L52" s="6">
+        <v>0</v>
+      </c>
+      <c r="M52" s="6">
         <v>11</v>
       </c>
-      <c r="N52" s="7">
-        <v>0</v>
-      </c>
-      <c r="O52" s="7">
-        <v>0</v>
-      </c>
-      <c r="P52" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="7">
-        <v>0</v>
-      </c>
-      <c r="R52" s="7">
+      <c r="N52" s="6">
+        <v>0</v>
+      </c>
+      <c r="O52" s="6">
+        <v>0</v>
+      </c>
+      <c r="P52" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>0</v>
+      </c>
+      <c r="R52" s="6">
         <v>0</v>
       </c>
       <c r="S52" s="2">
@@ -4071,8 +4073,8 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="S53" s="9" t="s">
-        <v>46</v>
+      <c r="S53" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -4246,13 +4248,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354560AC-9883-4771-8160-CFF399545C7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88258674-9A14-4044-824C-AC54C8DA494D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68F0FCE0-33CE-4CD4-8E86-3257F0E556A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CF713AC-A7F7-435B-8853-54172776FADF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AE36661-B3B5-4E2A-9FF3-A8158FE28628}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE71B6CE-E5FF-431E-AE81-6CE31E6E9441}"/>
 </file>